--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_C.B. GRANOLLERS.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_C.B. GRANOLLERS.xlsx
@@ -565,13 +565,13 @@
         <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>19.4516</v>
+        <v>12.1568</v>
       </c>
       <c r="E2" t="n">
-        <v>28.1276</v>
+        <v>23.3935</v>
       </c>
       <c r="F2" t="n">
-        <v>-8.676300000000001</v>
+        <v>-11.2372</v>
       </c>
       <c r="G2" t="n">
         <v>-4.545300000000001</v>
@@ -610,13 +610,13 @@
         <v>37.5058</v>
       </c>
       <c r="S2" t="n">
-        <v>13.6576</v>
+        <v>6.362500000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>9.4162</v>
+        <v>4.6823</v>
       </c>
       <c r="U2" t="n">
-        <v>4.2414</v>
+        <v>1.6802</v>
       </c>
       <c r="V2" t="n">
         <v>-10.9529</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C. HOMS LORENZO</t>
+          <t>G. PRAT PRUNA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="D3" t="n">
-        <v>13.5451</v>
+        <v>6.2851</v>
       </c>
       <c r="E3" t="n">
-        <v>13.2628</v>
+        <v>4.6088</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2823000000000002</v>
+        <v>1.676500000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>-13.0054</v>
+        <v>1.7548</v>
       </c>
       <c r="H3" t="n">
-        <v>-10.3853</v>
+        <v>6.378</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.620299999999999</v>
+        <v>-4.623</v>
       </c>
       <c r="J3" t="n">
-        <v>9.196599999999998</v>
+        <v>11.227</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7423000000000001</v>
+        <v>12.7409</v>
       </c>
       <c r="L3" t="n">
-        <v>8.454599999999999</v>
+        <v>-1.514</v>
       </c>
       <c r="M3" t="n">
-        <v>-22.2019</v>
+        <v>-9.472099999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>-11.128</v>
+        <v>-6.3629</v>
       </c>
       <c r="O3" t="n">
-        <v>-11.0746</v>
+        <v>-3.1091</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.9768</v>
+        <v>-3.3208</v>
       </c>
       <c r="Q3" t="n">
-        <v>-41.0215</v>
+        <v>-22.0737</v>
       </c>
       <c r="R3" t="n">
-        <v>40.0453</v>
+        <v>18.7529</v>
       </c>
       <c r="S3" t="n">
-        <v>10.7715</v>
+        <v>-5.6086</v>
       </c>
       <c r="T3" t="n">
-        <v>7.7404</v>
+        <v>-2.6593</v>
       </c>
       <c r="U3" t="n">
-        <v>3.0312</v>
+        <v>-2.9495</v>
       </c>
       <c r="V3" t="n">
-        <v>16.7555</v>
+        <v>13.4597</v>
       </c>
       <c r="W3" t="n">
-        <v>37.3475</v>
+        <v>18.1149</v>
       </c>
       <c r="X3" t="n">
-        <v>-20.5923</v>
+        <v>-4.6552</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>O. TOURE JABBY</t>
+          <t>C. HOMS LORENZO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D4" t="n">
-        <v>10.9561</v>
+        <v>3.000100000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.3480999999999999</v>
+        <v>6.081399999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>11.3043</v>
+        <v>-3.081400000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>11.3571</v>
+        <v>-13.0054</v>
       </c>
       <c r="H4" t="n">
-        <v>11.4201</v>
+        <v>-10.3853</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.06309999999999993</v>
+        <v>-2.620299999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>30.4639</v>
+        <v>9.196599999999998</v>
       </c>
       <c r="K4" t="n">
-        <v>23.6351</v>
+        <v>0.7423000000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>6.828899999999999</v>
+        <v>8.454599999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>-19.1068</v>
+        <v>-22.2019</v>
       </c>
       <c r="N4" t="n">
-        <v>-12.2147</v>
+        <v>-11.128</v>
       </c>
       <c r="O4" t="n">
-        <v>-6.891900000000001</v>
+        <v>-11.0746</v>
       </c>
       <c r="P4" t="n">
-        <v>-13.4787</v>
+        <v>-0.9768</v>
       </c>
       <c r="Q4" t="n">
-        <v>-43.7568</v>
+        <v>-41.0215</v>
       </c>
       <c r="R4" t="n">
-        <v>30.2781</v>
+        <v>40.0453</v>
       </c>
       <c r="S4" t="n">
-        <v>15.5011</v>
+        <v>0.2264999999999998</v>
       </c>
       <c r="T4" t="n">
-        <v>5.846500000000001</v>
+        <v>0.5590000000000002</v>
       </c>
       <c r="U4" t="n">
-        <v>9.6547</v>
+        <v>-0.3322000000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>-2.423900000000001</v>
+        <v>16.7555</v>
       </c>
       <c r="W4" t="n">
-        <v>7.0982</v>
+        <v>37.3475</v>
       </c>
       <c r="X4" t="n">
-        <v>-9.5221</v>
+        <v>-20.5923</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. PRAT PRUNA</t>
+          <t>M. TALAMINO COLLADO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1828</v>
+        <v>1.3023</v>
       </c>
       <c r="E5" t="n">
-        <v>1.535700000000001</v>
+        <v>2.4349</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3528</v>
+        <v>-1.1326</v>
       </c>
       <c r="G5" t="n">
-        <v>1.7548</v>
+        <v>2.6589</v>
       </c>
       <c r="H5" t="n">
-        <v>6.378</v>
+        <v>0.5548999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-4.623</v>
+        <v>2.104</v>
       </c>
       <c r="J5" t="n">
-        <v>11.227</v>
+        <v>3.5526</v>
       </c>
       <c r="K5" t="n">
-        <v>12.7409</v>
+        <v>1.0438</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.514</v>
+        <v>2.5089</v>
       </c>
       <c r="M5" t="n">
-        <v>-9.472099999999999</v>
+        <v>-0.8937</v>
       </c>
       <c r="N5" t="n">
-        <v>-6.3629</v>
+        <v>-0.4889</v>
       </c>
       <c r="O5" t="n">
-        <v>-3.1091</v>
+        <v>-0.4049</v>
       </c>
       <c r="P5" t="n">
-        <v>-3.3208</v>
+        <v>-0.586</v>
       </c>
       <c r="Q5" t="n">
-        <v>-22.0737</v>
+        <v>-0.9767</v>
       </c>
       <c r="R5" t="n">
-        <v>18.7529</v>
+        <v>0.3907</v>
       </c>
       <c r="S5" t="n">
-        <v>-10.7112</v>
+        <v>-0.2277</v>
       </c>
       <c r="T5" t="n">
-        <v>-5.7326</v>
+        <v>-0.141</v>
       </c>
       <c r="U5" t="n">
-        <v>-4.9785</v>
+        <v>-0.0867</v>
       </c>
       <c r="V5" t="n">
-        <v>13.4597</v>
+        <v>-0.5429</v>
       </c>
       <c r="W5" t="n">
-        <v>18.1149</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-4.6552</v>
+        <v>-0.5429</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. TALAMINO COLLADO</t>
+          <t>D. CABEZAS JURADO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0105</v>
+        <v>1.1101</v>
       </c>
       <c r="E6" t="n">
-        <v>2.3338</v>
+        <v>1.0985</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.3233</v>
+        <v>0.0116</v>
       </c>
       <c r="G6" t="n">
-        <v>2.6589</v>
+        <v>-0.0445</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5548999999999999</v>
+        <v>0.4948</v>
       </c>
       <c r="I6" t="n">
-        <v>2.104</v>
+        <v>-0.5393</v>
       </c>
       <c r="J6" t="n">
-        <v>3.5526</v>
+        <v>-0.0397</v>
       </c>
       <c r="K6" t="n">
-        <v>1.0438</v>
+        <v>0.6344</v>
       </c>
       <c r="L6" t="n">
-        <v>2.5089</v>
+        <v>-0.6741</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8937</v>
+        <v>-0.0049</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4889</v>
+        <v>-0.1397</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4049</v>
+        <v>0.1348</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.586</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3907</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5195</v>
+        <v>-0.064</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2421</v>
+        <v>-0.0805</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2774</v>
+        <v>0.0165</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.5429</v>
+        <v>1.2186</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5429</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. CABEZAS JURADO</t>
+          <t>P. DÍAZ JIMÉNEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9546</v>
+        <v>0.2916000000000003</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9974</v>
+        <v>1.7398</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0428</v>
+        <v>-1.4482</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.0445</v>
+        <v>-1.1852</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4948</v>
+        <v>0.2722</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5393</v>
+        <v>-1.4574</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.0397</v>
+        <v>1.1275</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6344</v>
+        <v>0.9657000000000002</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6741</v>
+        <v>0.1619</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0049</v>
+        <v>-2.3128</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1397</v>
+        <v>-0.6935</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1348</v>
+        <v>-1.6193</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.9767</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.1953</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.172</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2196</v>
+        <v>0.5001</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1816</v>
+        <v>-0.07900000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.038</v>
+        <v>0.579</v>
       </c>
       <c r="V7" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2186</v>
+        <v>0.8865</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.8864999999999998</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. DÍAZ JIMÉNEZ</t>
+          <t>F. PÉREZ CARRASCO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5029999999999999</v>
+        <v>0.1753</v>
       </c>
       <c r="E8" t="n">
-        <v>1.8408</v>
+        <v>0.0405</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.3379</v>
+        <v>0.1348</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.1852</v>
+        <v>0.1753</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2722</v>
+        <v>0.1348</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.4574</v>
+        <v>0.0405</v>
       </c>
       <c r="J8" t="n">
-        <v>1.1275</v>
+        <v>0.0405</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9657000000000002</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1619</v>
+        <v>0.0405</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.3128</v>
+        <v>0.1348</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6935</v>
+        <v>0.1348</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.6193</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.172</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7115</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.02209999999999995</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6894</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.8865</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.8864999999999998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. TORNÉ DELAURENS</t>
+          <t>C. FERNANDEZ BUFI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4376999999999995</v>
+        <v>-0.0529</v>
       </c>
       <c r="E9" t="n">
-        <v>17.2416</v>
+        <v>0.7169</v>
       </c>
       <c r="F9" t="n">
-        <v>-16.8039</v>
+        <v>-0.7698</v>
       </c>
       <c r="G9" t="n">
-        <v>-19.5057</v>
+        <v>0.7923</v>
       </c>
       <c r="H9" t="n">
-        <v>-20.0598</v>
+        <v>-0.1384</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5539000000000003</v>
+        <v>0.9307</v>
       </c>
       <c r="J9" t="n">
-        <v>11.7742</v>
+        <v>0.6625</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8206000000000002</v>
+        <v>0.0013</v>
       </c>
       <c r="L9" t="n">
-        <v>10.9535</v>
+        <v>0.6613</v>
       </c>
       <c r="M9" t="n">
-        <v>-31.2795</v>
+        <v>0.1298</v>
       </c>
       <c r="N9" t="n">
-        <v>-20.8803</v>
+        <v>-0.1397</v>
       </c>
       <c r="O9" t="n">
-        <v>-10.3992</v>
+        <v>0.2694</v>
       </c>
       <c r="P9" t="n">
-        <v>19.7296</v>
+        <v>0.3907</v>
       </c>
       <c r="Q9" t="n">
-        <v>-15.0412</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>34.7711</v>
+        <v>0.3907</v>
       </c>
       <c r="S9" t="n">
-        <v>10.8295</v>
+        <v>-0.0172</v>
       </c>
       <c r="T9" t="n">
-        <v>14.5772</v>
+        <v>0.0544</v>
       </c>
       <c r="U9" t="n">
-        <v>-3.748</v>
+        <v>-0.0716</v>
       </c>
       <c r="V9" t="n">
-        <v>-10.6161</v>
+        <v>-1.2186</v>
       </c>
       <c r="W9" t="n">
-        <v>5.931099999999999</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-16.5473</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>F. PÉREZ CARRASCO</t>
+          <t>M. MONTANER BRIERA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1753</v>
+        <v>-0.3184</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0405</v>
+        <v>0.3433</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1348</v>
+        <v>-0.6617</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1753</v>
+        <v>-0.196</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1348</v>
+        <v>0.7079</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0405</v>
+        <v>-0.9039</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0405</v>
+        <v>1.0228</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>0.9824000000000001</v>
       </c>
       <c r="L10" t="n">
         <v>0.0405</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1348</v>
+        <v>-1.2188</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1348</v>
+        <v>-0.2745</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>-0.9443</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>0.586</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>0.2683</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>0.2972</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>-0.0289</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. MONTANER BRIERA</t>
+          <t>E. VÁZQUEZ MARESMA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0588</v>
+        <v>-0.3185</v>
       </c>
       <c r="E11" t="n">
-        <v>0.7478</v>
+        <v>-0.7185</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.6889</v>
+        <v>0.4</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.196</v>
+        <v>0.3617</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7079</v>
+        <v>-0.2589</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.9039</v>
+        <v>0.6206</v>
       </c>
       <c r="J11" t="n">
-        <v>1.0228</v>
+        <v>0.6413</v>
       </c>
       <c r="K11" t="n">
-        <v>0.9824000000000001</v>
+        <v>0.0205</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0405</v>
+        <v>0.6208</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.2188</v>
+        <v>-0.2795</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2745</v>
+        <v>-0.2793</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.9443</v>
+        <v>-0.0002</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.3907</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q11" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R11" t="n">
-        <v>0.586</v>
+        <v>0.7814</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6455</v>
+        <v>-0.4849</v>
       </c>
       <c r="T11" t="n">
-        <v>0.7016</v>
+        <v>-0.3831</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0561</v>
+        <v>-0.1018</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>C. FERNANDEZ BUFI</t>
+          <t>F. REYES ARANDA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.09950000000000001</v>
+        <v>-1.1469</v>
       </c>
       <c r="E12" t="n">
-        <v>0.6158</v>
+        <v>-1.8014</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.7153</v>
+        <v>0.6542</v>
       </c>
       <c r="G12" t="n">
-        <v>0.7923</v>
+        <v>-0.7487999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.1384</v>
+        <v>-2.4341</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9307</v>
+        <v>1.6854</v>
       </c>
       <c r="J12" t="n">
-        <v>0.6625</v>
+        <v>-0.5240999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0013</v>
+        <v>-1.9404</v>
       </c>
       <c r="L12" t="n">
-        <v>0.6613</v>
+        <v>1.4164</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1298</v>
+        <v>-0.2247</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1397</v>
+        <v>-0.4936999999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>0.2694</v>
+        <v>0.2691</v>
       </c>
       <c r="P12" t="n">
-        <v>0.3907</v>
+        <v>0.5859</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-1.172</v>
       </c>
       <c r="R12" t="n">
-        <v>0.3907</v>
+        <v>1.758</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0639</v>
+        <v>-1.2614</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0467</v>
+        <v>-0.3822</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0171</v>
+        <v>-0.8792</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.2186</v>
+        <v>0.2772</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>E. VÁZQUEZ MARESMA</t>
+          <t>M. BALLÚS TORRAS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.4196</v>
+        <v>-1.2205</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.8196</v>
+        <v>0.5276999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4</v>
+        <v>-1.7483</v>
       </c>
       <c r="G13" t="n">
-        <v>0.3617</v>
+        <v>-2.1278</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.2589</v>
+        <v>3.2131</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6206</v>
+        <v>-5.3409</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6413</v>
+        <v>3.1122</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0205</v>
+        <v>4.4053</v>
       </c>
       <c r="L13" t="n">
-        <v>0.6208</v>
+        <v>-1.2929</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.2795</v>
+        <v>-5.2401</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.2793</v>
+        <v>-1.1921</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.0002</v>
+        <v>-4.048</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.1953</v>
+        <v>0.3907</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.9767</v>
+        <v>-3.9068</v>
       </c>
       <c r="R13" t="n">
-        <v>0.7814</v>
+        <v>4.297499999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.586</v>
+        <v>0.4835999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4842</v>
+        <v>0.4357</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1018</v>
+        <v>0.04799999999999998</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.03289999999999993</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>0.8864999999999998</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-0.8535999999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>F. REYES ARANDA</t>
+          <t>O. TOURE JABBY</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.7966</v>
+        <v>-1.353200000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.2058</v>
+        <v>-5.588399999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4091</v>
+        <v>4.235200000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.7487999999999999</v>
+        <v>11.3571</v>
       </c>
       <c r="H14" t="n">
-        <v>-2.4341</v>
+        <v>11.4201</v>
       </c>
       <c r="I14" t="n">
-        <v>1.6854</v>
+        <v>-0.06309999999999993</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.5240999999999999</v>
+        <v>30.4639</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.9404</v>
+        <v>23.6351</v>
       </c>
       <c r="L14" t="n">
-        <v>1.4164</v>
+        <v>6.828899999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.2247</v>
+        <v>-19.1068</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.4936999999999999</v>
+        <v>-12.2147</v>
       </c>
       <c r="O14" t="n">
-        <v>0.2691</v>
+        <v>-6.891900000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>0.5859</v>
+        <v>-13.4787</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.172</v>
+        <v>-43.7568</v>
       </c>
       <c r="R14" t="n">
-        <v>1.758</v>
+        <v>30.2781</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.911</v>
+        <v>3.192299999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7867</v>
+        <v>0.6063999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.1243</v>
+        <v>2.5856</v>
       </c>
       <c r="V14" t="n">
-        <v>0.2772</v>
+        <v>-2.423900000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>0.2772</v>
+        <v>7.0982</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-9.5221</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. BALLÚS TORRAS</t>
+          <t>A. VIÑALLONGA GOMEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,70 +1576,70 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="D15" t="n">
-        <v>-3.4909</v>
+        <v>-1.601</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.1707</v>
+        <v>-2.5656</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.3202</v>
+        <v>0.9645999999999995</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.1278</v>
+        <v>-2.612499999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>3.2131</v>
+        <v>-8.788500000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>-5.3409</v>
+        <v>6.176</v>
       </c>
       <c r="J15" t="n">
-        <v>3.1122</v>
+        <v>31.8298</v>
       </c>
       <c r="K15" t="n">
-        <v>4.4053</v>
+        <v>16.1958</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.2929</v>
+        <v>15.6337</v>
       </c>
       <c r="M15" t="n">
-        <v>-5.2401</v>
+        <v>-34.4417</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.1921</v>
+        <v>-24.9843</v>
       </c>
       <c r="O15" t="n">
-        <v>-4.048</v>
+        <v>-9.457699999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>0.3907</v>
+        <v>-4.883399999999999</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.9068</v>
+        <v>-49.8122</v>
       </c>
       <c r="R15" t="n">
-        <v>4.297499999999999</v>
+        <v>44.9288</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.7868</v>
+        <v>-10.629</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.2626</v>
+        <v>-5.4667</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5241</v>
+        <v>-5.1619</v>
       </c>
       <c r="V15" t="n">
-        <v>0.03289999999999993</v>
+        <v>16.5235</v>
       </c>
       <c r="W15" t="n">
-        <v>0.8864999999999998</v>
+        <v>20.8839</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.8535999999999999</v>
+        <v>-4.3606</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>20</v>
       </c>
       <c r="D16" t="n">
-        <v>-7.1365</v>
+        <v>-3.5362</v>
       </c>
       <c r="E16" t="n">
-        <v>-10.6854</v>
+        <v>-6.966299999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>3.548699999999999</v>
+        <v>3.430099999999999</v>
       </c>
       <c r="G16" t="n">
         <v>-1.948199999999999</v>
@@ -1702,13 +1702,13 @@
         <v>22.2691</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.7704</v>
+        <v>1.8301</v>
       </c>
       <c r="T16" t="n">
-        <v>-3.4179</v>
+        <v>0.3008</v>
       </c>
       <c r="U16" t="n">
-        <v>1.6475</v>
+        <v>1.5292</v>
       </c>
       <c r="V16" t="n">
         <v>-0.4881</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. PEIRO COSMO</t>
+          <t>A. MARTÍN ADELANTADO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,76 +1732,76 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D17" t="n">
-        <v>-9.740400000000001</v>
+        <v>-6.0782</v>
       </c>
       <c r="E17" t="n">
-        <v>-6.0268</v>
+        <v>-0.3617000000000006</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.7136</v>
+        <v>-5.7163</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.9527</v>
+        <v>-12.4205</v>
       </c>
       <c r="H17" t="n">
-        <v>1.5983</v>
+        <v>-6.3161</v>
       </c>
       <c r="I17" t="n">
-        <v>-3.5505</v>
+        <v>-6.1044</v>
       </c>
       <c r="J17" t="n">
-        <v>9.0733</v>
+        <v>7.2849</v>
       </c>
       <c r="K17" t="n">
-        <v>8.0311</v>
+        <v>3.9421</v>
       </c>
       <c r="L17" t="n">
-        <v>1.0423</v>
+        <v>3.3428</v>
       </c>
       <c r="M17" t="n">
-        <v>-11.0258</v>
+        <v>-19.7056</v>
       </c>
       <c r="N17" t="n">
-        <v>-6.433</v>
+        <v>-10.2582</v>
       </c>
       <c r="O17" t="n">
-        <v>-4.5931</v>
+        <v>-9.447199999999999</v>
       </c>
       <c r="P17" t="n">
-        <v>0.7813000000000001</v>
+        <v>5.4697</v>
       </c>
       <c r="Q17" t="n">
-        <v>-17.9712</v>
+        <v>-8.7904</v>
       </c>
       <c r="R17" t="n">
-        <v>18.7531</v>
+        <v>14.2601</v>
       </c>
       <c r="S17" t="n">
-        <v>-3.573</v>
+        <v>2.0919</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.619</v>
+        <v>0.5343000000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.9537</v>
+        <v>1.5576</v>
       </c>
       <c r="V17" t="n">
-        <v>-4.9962</v>
+        <v>-1.2191</v>
       </c>
       <c r="W17" t="n">
-        <v>4.4904</v>
+        <v>0.6093</v>
       </c>
       <c r="X17" t="n">
-        <v>-9.486799999999999</v>
+        <v>-1.8285</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. MARTÍN ADELANTADO</t>
+          <t>M. TORNÉ DELAURENS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,76 +1810,76 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D18" t="n">
-        <v>-13.7109</v>
+        <v>-6.305</v>
       </c>
       <c r="E18" t="n">
-        <v>-5.2751</v>
+        <v>6.5419</v>
       </c>
       <c r="F18" t="n">
-        <v>-8.4359</v>
+        <v>-12.8466</v>
       </c>
       <c r="G18" t="n">
-        <v>-12.4205</v>
+        <v>-19.5057</v>
       </c>
       <c r="H18" t="n">
-        <v>-6.3161</v>
+        <v>-20.0598</v>
       </c>
       <c r="I18" t="n">
-        <v>-6.1044</v>
+        <v>0.5539000000000003</v>
       </c>
       <c r="J18" t="n">
-        <v>7.2849</v>
+        <v>11.7742</v>
       </c>
       <c r="K18" t="n">
-        <v>3.9421</v>
+        <v>0.8206000000000002</v>
       </c>
       <c r="L18" t="n">
-        <v>3.3428</v>
+        <v>10.9535</v>
       </c>
       <c r="M18" t="n">
-        <v>-19.7056</v>
+        <v>-31.2795</v>
       </c>
       <c r="N18" t="n">
-        <v>-10.2582</v>
+        <v>-20.8803</v>
       </c>
       <c r="O18" t="n">
-        <v>-9.447199999999999</v>
+        <v>-10.3992</v>
       </c>
       <c r="P18" t="n">
-        <v>5.4697</v>
+        <v>19.7296</v>
       </c>
       <c r="Q18" t="n">
-        <v>-8.7904</v>
+        <v>-15.0412</v>
       </c>
       <c r="R18" t="n">
-        <v>14.2601</v>
+        <v>34.7711</v>
       </c>
       <c r="S18" t="n">
-        <v>-5.540900000000001</v>
+        <v>4.0867</v>
       </c>
       <c r="T18" t="n">
-        <v>-4.3789</v>
+        <v>3.8775</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.1618</v>
+        <v>0.2095000000000001</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.2191</v>
+        <v>-10.6161</v>
       </c>
       <c r="W18" t="n">
-        <v>0.6093</v>
+        <v>5.931099999999999</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.8285</v>
+        <v>-16.5473</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. SALMERON SEGU</t>
+          <t>A. PEIRO COSMO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1888,76 +1888,76 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D19" t="n">
-        <v>-14.2646</v>
+        <v>-6.453600000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.508300000000001</v>
+        <v>-4.329000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>-10.7565</v>
+        <v>-2.1245</v>
       </c>
       <c r="G19" t="n">
-        <v>-12.0746</v>
+        <v>-1.9527</v>
       </c>
       <c r="H19" t="n">
-        <v>-4.1284</v>
+        <v>1.5983</v>
       </c>
       <c r="I19" t="n">
-        <v>-7.945699999999999</v>
+        <v>-3.5505</v>
       </c>
       <c r="J19" t="n">
-        <v>14.0221</v>
+        <v>9.0733</v>
       </c>
       <c r="K19" t="n">
-        <v>12.2444</v>
+        <v>8.0311</v>
       </c>
       <c r="L19" t="n">
-        <v>1.7774</v>
+        <v>1.0423</v>
       </c>
       <c r="M19" t="n">
-        <v>-26.0964</v>
+        <v>-11.0258</v>
       </c>
       <c r="N19" t="n">
-        <v>-16.3729</v>
+        <v>-6.433</v>
       </c>
       <c r="O19" t="n">
-        <v>-9.7239</v>
+        <v>-4.5931</v>
       </c>
       <c r="P19" t="n">
-        <v>5.8605</v>
+        <v>0.7813000000000001</v>
       </c>
       <c r="Q19" t="n">
-        <v>-23.6363</v>
+        <v>-17.9712</v>
       </c>
       <c r="R19" t="n">
-        <v>29.4971</v>
+        <v>18.7531</v>
       </c>
       <c r="S19" t="n">
-        <v>3.0793</v>
+        <v>-0.2860000000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>4.0498</v>
+        <v>0.07839999999999997</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.9708000000000001</v>
+        <v>-0.3647</v>
       </c>
       <c r="V19" t="n">
-        <v>-11.13</v>
+        <v>-4.9962</v>
       </c>
       <c r="W19" t="n">
-        <v>2.055899999999999</v>
+        <v>4.4904</v>
       </c>
       <c r="X19" t="n">
-        <v>-13.186</v>
+        <v>-9.486799999999999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. VIÑALLONGA GOMEZ</t>
+          <t>O. HERAS FLECHA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1966,70 +1966,70 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D20" t="n">
-        <v>-19.5257</v>
+        <v>-9.1546</v>
       </c>
       <c r="E20" t="n">
-        <v>-14.0301</v>
+        <v>5.104600000000002</v>
       </c>
       <c r="F20" t="n">
-        <v>-5.495599999999999</v>
+        <v>-14.2593</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.612499999999999</v>
+        <v>-10.1346</v>
       </c>
       <c r="H20" t="n">
-        <v>-8.788500000000001</v>
+        <v>-5.1165</v>
       </c>
       <c r="I20" t="n">
-        <v>6.176</v>
+        <v>-5.017900000000001</v>
       </c>
       <c r="J20" t="n">
-        <v>31.8298</v>
+        <v>23.3241</v>
       </c>
       <c r="K20" t="n">
-        <v>16.1958</v>
+        <v>19.0201</v>
       </c>
       <c r="L20" t="n">
-        <v>15.6337</v>
+        <v>4.3043</v>
       </c>
       <c r="M20" t="n">
-        <v>-34.4417</v>
+        <v>-33.4586</v>
       </c>
       <c r="N20" t="n">
-        <v>-24.9843</v>
+        <v>-24.1365</v>
       </c>
       <c r="O20" t="n">
-        <v>-9.457699999999999</v>
+        <v>-9.321999999999999</v>
       </c>
       <c r="P20" t="n">
-        <v>-4.883399999999999</v>
+        <v>-0.7815000000000001</v>
       </c>
       <c r="Q20" t="n">
-        <v>-49.8122</v>
+        <v>-40.8265</v>
       </c>
       <c r="R20" t="n">
-        <v>44.9288</v>
+        <v>40.0455</v>
       </c>
       <c r="S20" t="n">
-        <v>-28.5536</v>
+        <v>-11.709</v>
       </c>
       <c r="T20" t="n">
-        <v>-16.9313</v>
+        <v>-3.8732</v>
       </c>
       <c r="U20" t="n">
-        <v>-11.6222</v>
+        <v>-7.8359</v>
       </c>
       <c r="V20" t="n">
-        <v>16.5235</v>
+        <v>13.471</v>
       </c>
       <c r="W20" t="n">
-        <v>20.8839</v>
+        <v>26.4808</v>
       </c>
       <c r="X20" t="n">
-        <v>-4.3606</v>
+        <v>-13.0098</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>26</v>
       </c>
       <c r="D21" t="n">
-        <v>-21.4757</v>
+        <v>-13.7192</v>
       </c>
       <c r="E21" t="n">
-        <v>-20.3704</v>
+        <v>-16.4093</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.105599999999999</v>
+        <v>2.6899</v>
       </c>
       <c r="G21" t="n">
         <v>-15.9332</v>
@@ -2092,13 +2092,13 @@
         <v>44.343</v>
       </c>
       <c r="S21" t="n">
-        <v>-12.6283</v>
+        <v>-4.871700000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>-5.6285</v>
+        <v>-1.6672</v>
       </c>
       <c r="U21" t="n">
-        <v>-6.999700000000001</v>
+        <v>-3.2044</v>
       </c>
       <c r="V21" t="n">
         <v>16.4618</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>O. HERAS FLECHA</t>
+          <t>M. SALMERON SEGU</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2122,70 +2122,70 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D22" t="n">
-        <v>-25.0693</v>
+        <v>-14.3955</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.9623</v>
+        <v>-5.673400000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>-22.1072</v>
+        <v>-8.722100000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>-10.1346</v>
+        <v>-12.0746</v>
       </c>
       <c r="H22" t="n">
-        <v>-5.1165</v>
+        <v>-4.1284</v>
       </c>
       <c r="I22" t="n">
-        <v>-5.017900000000001</v>
+        <v>-7.945699999999999</v>
       </c>
       <c r="J22" t="n">
-        <v>23.3241</v>
+        <v>14.0221</v>
       </c>
       <c r="K22" t="n">
-        <v>19.0201</v>
+        <v>12.2444</v>
       </c>
       <c r="L22" t="n">
-        <v>4.3043</v>
+        <v>1.7774</v>
       </c>
       <c r="M22" t="n">
-        <v>-33.4586</v>
+        <v>-26.0964</v>
       </c>
       <c r="N22" t="n">
-        <v>-24.1365</v>
+        <v>-16.3729</v>
       </c>
       <c r="O22" t="n">
-        <v>-9.321999999999999</v>
+        <v>-9.7239</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.7815000000000001</v>
+        <v>5.8605</v>
       </c>
       <c r="Q22" t="n">
-        <v>-40.8265</v>
+        <v>-23.6363</v>
       </c>
       <c r="R22" t="n">
-        <v>40.0455</v>
+        <v>29.4971</v>
       </c>
       <c r="S22" t="n">
-        <v>-27.6244</v>
+        <v>2.9486</v>
       </c>
       <c r="T22" t="n">
-        <v>-11.9406</v>
+        <v>1.8848</v>
       </c>
       <c r="U22" t="n">
-        <v>-15.6834</v>
+        <v>1.0638</v>
       </c>
       <c r="V22" t="n">
-        <v>13.471</v>
+        <v>-11.13</v>
       </c>
       <c r="W22" t="n">
-        <v>26.4808</v>
+        <v>2.055899999999999</v>
       </c>
       <c r="X22" t="n">
-        <v>-13.0098</v>
+        <v>-13.186</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>26</v>
       </c>
       <c r="D23" t="n">
-        <v>-68.45420000000001</v>
+        <v>-41.33240000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.6588000000000003</v>
+        <v>8.218199999999992</v>
       </c>
       <c r="F23" t="n">
-        <v>-67.7966</v>
+        <v>-49.55110000000001</v>
       </c>
       <c r="G23" t="n">
         <v>-81.3349</v>
@@ -2218,7 +2218,7 @@
         <v>-63.8168</v>
       </c>
       <c r="I23" t="n">
-        <v>-17.51659999999999</v>
+        <v>-17.5166</v>
       </c>
       <c r="J23" t="n">
         <v>209.5115</v>
@@ -2248,16 +2248,16 @@
         <v>384.8262</v>
       </c>
       <c r="S23" t="n">
-        <v>-40.29259999999999</v>
+        <v>-13.1689</v>
       </c>
       <c r="T23" t="n">
-        <v>-10.29889999999999</v>
+        <v>-1.421399999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>-29.9927</v>
+        <v>-11.7474</v>
       </c>
       <c r="V23" t="n">
-        <v>34.6124</v>
+        <v>34.61240000000001</v>
       </c>
       <c r="W23" t="n">
         <v>166.3944</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_C.B. GRANOLLERS.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_C.B. GRANOLLERS.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X23"/>
+  <dimension ref="A1:X28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. MURCIANO PUJADAS</t>
+          <t>A. VIÑALLONGA GOMEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D2" t="n">
-        <v>12.1568</v>
+        <v>26.2682</v>
       </c>
       <c r="E2" t="n">
-        <v>23.3935</v>
+        <v>26.2682</v>
       </c>
       <c r="F2" t="n">
-        <v>-11.2372</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-4.545300000000001</v>
+        <v>26.2682</v>
       </c>
       <c r="H2" t="n">
-        <v>-15.3584</v>
+        <v>14.7356</v>
       </c>
       <c r="I2" t="n">
-        <v>10.8131</v>
+        <v>11.5328</v>
       </c>
       <c r="J2" t="n">
-        <v>29.6056</v>
+        <v>26.2682</v>
       </c>
       <c r="K2" t="n">
-        <v>11.4936</v>
+        <v>14.7356</v>
       </c>
       <c r="L2" t="n">
-        <v>18.1118</v>
+        <v>11.5328</v>
       </c>
       <c r="M2" t="n">
-        <v>-34.1511</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-26.8524</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-7.298999999999999</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>21.2924</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-16.2131</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>37.5058</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>6.362500000000001</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>4.6823</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1.6802</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>-10.9529</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>5.3191</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-16.272</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>G. PRAT PRUNA</t>
+          <t>A. MURCIANO PUJADAS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>6.2851</v>
+        <v>12.1568</v>
       </c>
       <c r="E3" t="n">
-        <v>4.6088</v>
+        <v>23.3935</v>
       </c>
       <c r="F3" t="n">
-        <v>1.676500000000001</v>
+        <v>-11.2372</v>
       </c>
       <c r="G3" t="n">
-        <v>1.7548</v>
+        <v>-4.545300000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>6.378</v>
+        <v>-15.3584</v>
       </c>
       <c r="I3" t="n">
-        <v>-4.623</v>
+        <v>10.8131</v>
       </c>
       <c r="J3" t="n">
-        <v>11.227</v>
+        <v>29.6056</v>
       </c>
       <c r="K3" t="n">
-        <v>12.7409</v>
+        <v>11.4936</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.514</v>
+        <v>18.1118</v>
       </c>
       <c r="M3" t="n">
-        <v>-9.472099999999999</v>
+        <v>-34.1511</v>
       </c>
       <c r="N3" t="n">
-        <v>-6.3629</v>
+        <v>-26.8524</v>
       </c>
       <c r="O3" t="n">
-        <v>-3.1091</v>
+        <v>-7.298999999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>-3.3208</v>
+        <v>21.2924</v>
       </c>
       <c r="Q3" t="n">
-        <v>-22.0737</v>
+        <v>-16.2131</v>
       </c>
       <c r="R3" t="n">
-        <v>18.7529</v>
+        <v>37.5058</v>
       </c>
       <c r="S3" t="n">
-        <v>-5.6086</v>
+        <v>6.362500000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>-2.6593</v>
+        <v>4.6823</v>
       </c>
       <c r="U3" t="n">
-        <v>-2.9495</v>
+        <v>1.6802</v>
       </c>
       <c r="V3" t="n">
-        <v>13.4597</v>
+        <v>-10.9529</v>
       </c>
       <c r="W3" t="n">
-        <v>18.1149</v>
+        <v>5.3191</v>
       </c>
       <c r="X3" t="n">
-        <v>-4.6552</v>
+        <v>-16.272</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C. HOMS LORENZO</t>
+          <t>M. TORNÉ DELAURENS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D4" t="n">
-        <v>3.000100000000001</v>
+        <v>11.261</v>
       </c>
       <c r="E4" t="n">
-        <v>6.081399999999999</v>
+        <v>11.261</v>
       </c>
       <c r="F4" t="n">
-        <v>-3.081400000000001</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-13.0054</v>
+        <v>11.261</v>
       </c>
       <c r="H4" t="n">
-        <v>-10.3853</v>
+        <v>2.763</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.620299999999999</v>
+        <v>8.497999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>9.196599999999998</v>
+        <v>11.261</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7423000000000001</v>
+        <v>2.763</v>
       </c>
       <c r="L4" t="n">
-        <v>8.454599999999999</v>
+        <v>8.497999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>-22.2019</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-11.128</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-11.0746</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.9768</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-41.0215</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>40.0453</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2264999999999998</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5590000000000002</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3322000000000001</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>16.7555</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>37.3475</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-20.5923</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. TALAMINO COLLADO</t>
+          <t>A. MARTÍN ADELANTADO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3023</v>
+        <v>10.0607</v>
       </c>
       <c r="E5" t="n">
-        <v>2.4349</v>
+        <v>10.0607</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.1326</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>2.6589</v>
+        <v>10.0607</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5548999999999999</v>
+        <v>3.991</v>
       </c>
       <c r="I5" t="n">
-        <v>2.104</v>
+        <v>6.07</v>
       </c>
       <c r="J5" t="n">
-        <v>3.5526</v>
+        <v>10.0607</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0438</v>
+        <v>3.991</v>
       </c>
       <c r="L5" t="n">
-        <v>2.5089</v>
+        <v>6.07</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.8937</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4889</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4049</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.586</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3907</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2277</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.141</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0867</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.5429</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5429</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. CABEZAS JURADO</t>
+          <t>G. PRAT PRUNA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1101</v>
+        <v>6.2851</v>
       </c>
       <c r="E6" t="n">
-        <v>1.0985</v>
+        <v>4.6088</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0116</v>
+        <v>1.676500000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0445</v>
+        <v>1.7548</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4948</v>
+        <v>6.378</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5393</v>
+        <v>-4.623</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.0397</v>
+        <v>11.227</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6344</v>
+        <v>12.7409</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6741</v>
+        <v>-1.514</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0049</v>
+        <v>-9.472099999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1397</v>
+        <v>-6.3629</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1348</v>
+        <v>-3.1091</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-3.3208</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-22.0737</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>18.7529</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.064</v>
+        <v>-5.6086</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0805</v>
+        <v>-2.6593</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0165</v>
+        <v>-2.9495</v>
       </c>
       <c r="V6" t="n">
-        <v>1.2186</v>
+        <v>13.4597</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2186</v>
+        <v>18.1149</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-4.6552</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. DÍAZ JIMÉNEZ</t>
+          <t>C. HOMS LORENZO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2916000000000003</v>
+        <v>3.000100000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>1.7398</v>
+        <v>6.081399999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.4482</v>
+        <v>-3.081400000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.1852</v>
+        <v>-13.0054</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2722</v>
+        <v>-10.3853</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.4574</v>
+        <v>-2.620299999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>1.1275</v>
+        <v>9.196599999999998</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9657000000000002</v>
+        <v>0.7423000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1619</v>
+        <v>8.454599999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.3128</v>
+        <v>-22.2019</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6935</v>
+        <v>-11.128</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.6193</v>
+        <v>-11.0746</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9767</v>
+        <v>-0.9768</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.1953</v>
+        <v>-41.0215</v>
       </c>
       <c r="R7" t="n">
-        <v>1.172</v>
+        <v>40.0453</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5001</v>
+        <v>0.2264999999999998</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.07900000000000001</v>
+        <v>0.5590000000000002</v>
       </c>
       <c r="U7" t="n">
-        <v>0.579</v>
+        <v>-0.3322000000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>16.7555</v>
       </c>
       <c r="W7" t="n">
-        <v>0.8865</v>
+        <v>37.3475</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.8864999999999998</v>
+        <v>-20.5923</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>F. PÉREZ CARRASCO</t>
+          <t>M. TALAMINO COLLADO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1753</v>
+        <v>1.3023</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0405</v>
+        <v>2.4349</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1348</v>
+        <v>-1.1326</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1753</v>
+        <v>2.6589</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1348</v>
+        <v>0.5548999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0405</v>
+        <v>2.104</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0405</v>
+        <v>3.5526</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1.0438</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0405</v>
+        <v>2.5089</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1348</v>
+        <v>-0.8937</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1348</v>
+        <v>-0.4889</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>-0.4049</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-0.586</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>0.3907</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>-0.2277</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>-0.141</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>-0.0867</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.5429</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.5429</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C. FERNANDEZ BUFI</t>
+          <t>M. BALLÚS TORRAS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0529</v>
+        <v>1.221</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7169</v>
+        <v>1.221</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7698</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7923</v>
+        <v>1.221</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1384</v>
+        <v>0.614</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9307</v>
+        <v>0.607</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6625</v>
+        <v>1.221</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0013</v>
+        <v>0.614</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6613</v>
+        <v>0.607</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1298</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1397</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2694</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3907</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3907</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0172</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0544</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0716</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. MONTANER BRIERA</t>
+          <t>D. CABEZAS JURADO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.3184</v>
+        <v>1.1101</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3433</v>
+        <v>1.0985</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6617</v>
+        <v>0.0116</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.196</v>
+        <v>-0.0445</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7079</v>
+        <v>0.4948</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.9039</v>
+        <v>-0.5393</v>
       </c>
       <c r="J10" t="n">
-        <v>1.0228</v>
+        <v>-0.0397</v>
       </c>
       <c r="K10" t="n">
-        <v>0.9824000000000001</v>
+        <v>0.6344</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0405</v>
+        <v>-0.6741</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.2188</v>
+        <v>-0.0049</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2745</v>
+        <v>-0.1397</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.9443</v>
+        <v>0.1348</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.3907</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2683</v>
+        <v>-0.064</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2972</v>
+        <v>-0.0805</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0289</v>
+        <v>0.0165</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>E. VÁZQUEZ MARESMA</t>
+          <t>P. DÍAZ JIMÉNEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.3185</v>
+        <v>0.307</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.7185</v>
+        <v>0.307</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3617</v>
+        <v>0.307</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.2589</v>
+        <v>0.307</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6206</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6413</v>
+        <v>0.307</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0205</v>
+        <v>0.307</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6208</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.2795</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2793</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.0002</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4849</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3831</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1018</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>F. REYES ARANDA</t>
+          <t>F. PEREZ CARRASCO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,67 +1342,67 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.1469</v>
+        <v>0.1753</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.8014</v>
+        <v>0.0405</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6542</v>
+        <v>0.1348</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.7487999999999999</v>
+        <v>0.1753</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.4341</v>
+        <v>0.1348</v>
       </c>
       <c r="I12" t="n">
-        <v>1.6854</v>
+        <v>0.0405</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.5240999999999999</v>
+        <v>0.0405</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.9404</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1.4164</v>
+        <v>0.0405</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.2247</v>
+        <v>0.1348</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.4936999999999999</v>
+        <v>0.1348</v>
       </c>
       <c r="O12" t="n">
-        <v>0.2691</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>0.5859</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.172</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.758</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.2614</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3822</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.8792</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. BALLÚS TORRAS</t>
+          <t>P. DIAZ JIMENEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.2205</v>
+        <v>-0.01539999999999986</v>
       </c>
       <c r="E13" t="n">
-        <v>0.5276999999999999</v>
+        <v>1.4328</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.7483</v>
+        <v>-1.4482</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.1278</v>
+        <v>-1.4921</v>
       </c>
       <c r="H13" t="n">
-        <v>3.2131</v>
+        <v>-0.03479999999999994</v>
       </c>
       <c r="I13" t="n">
-        <v>-5.3409</v>
+        <v>-1.4574</v>
       </c>
       <c r="J13" t="n">
-        <v>3.1122</v>
+        <v>0.8204999999999998</v>
       </c>
       <c r="K13" t="n">
-        <v>4.4053</v>
+        <v>0.6586999999999998</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.2929</v>
+        <v>0.1619</v>
       </c>
       <c r="M13" t="n">
-        <v>-5.2401</v>
+        <v>-2.3128</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.1921</v>
+        <v>-0.6935</v>
       </c>
       <c r="O13" t="n">
-        <v>-4.048</v>
+        <v>-1.6193</v>
       </c>
       <c r="P13" t="n">
-        <v>0.3907</v>
+        <v>0.9767</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.9068</v>
+        <v>-0.1953</v>
       </c>
       <c r="R13" t="n">
-        <v>4.297499999999999</v>
+        <v>1.172</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4835999999999999</v>
+        <v>0.5001</v>
       </c>
       <c r="T13" t="n">
-        <v>0.4357</v>
+        <v>-0.07900000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>0.04799999999999998</v>
+        <v>0.579</v>
       </c>
       <c r="V13" t="n">
-        <v>0.03289999999999993</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>0.8864999999999998</v>
+        <v>0.8865</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.8535999999999999</v>
+        <v>-0.8864999999999998</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>O. TOURE JABBY</t>
+          <t>C. FERNANDEZ BUFI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.353200000000001</v>
+        <v>-0.0529</v>
       </c>
       <c r="E14" t="n">
-        <v>-5.588399999999999</v>
+        <v>0.7169</v>
       </c>
       <c r="F14" t="n">
-        <v>4.235200000000001</v>
+        <v>-0.7698</v>
       </c>
       <c r="G14" t="n">
-        <v>11.3571</v>
+        <v>0.7923</v>
       </c>
       <c r="H14" t="n">
-        <v>11.4201</v>
+        <v>-0.1384</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.06309999999999993</v>
+        <v>0.9307</v>
       </c>
       <c r="J14" t="n">
-        <v>30.4639</v>
+        <v>0.6625</v>
       </c>
       <c r="K14" t="n">
-        <v>23.6351</v>
+        <v>0.0013</v>
       </c>
       <c r="L14" t="n">
-        <v>6.828899999999999</v>
+        <v>0.6613</v>
       </c>
       <c r="M14" t="n">
-        <v>-19.1068</v>
+        <v>0.1298</v>
       </c>
       <c r="N14" t="n">
-        <v>-12.2147</v>
+        <v>-0.1397</v>
       </c>
       <c r="O14" t="n">
-        <v>-6.891900000000001</v>
+        <v>0.2694</v>
       </c>
       <c r="P14" t="n">
-        <v>-13.4787</v>
+        <v>0.3907</v>
       </c>
       <c r="Q14" t="n">
-        <v>-43.7568</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>30.2781</v>
+        <v>0.3907</v>
       </c>
       <c r="S14" t="n">
-        <v>3.192299999999999</v>
+        <v>-0.0172</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6063999999999999</v>
+        <v>0.0544</v>
       </c>
       <c r="U14" t="n">
-        <v>2.5856</v>
+        <v>-0.0716</v>
       </c>
       <c r="V14" t="n">
-        <v>-2.423900000000001</v>
+        <v>-1.2186</v>
       </c>
       <c r="W14" t="n">
-        <v>7.0982</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-9.5221</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. VIÑALLONGA GOMEZ</t>
+          <t>M. MONTANER BRIERA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.601</v>
+        <v>-0.3184</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.5656</v>
+        <v>0.3433</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9645999999999995</v>
+        <v>-0.6617</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.612499999999999</v>
+        <v>-0.196</v>
       </c>
       <c r="H15" t="n">
-        <v>-8.788500000000001</v>
+        <v>0.7079</v>
       </c>
       <c r="I15" t="n">
-        <v>6.176</v>
+        <v>-0.9039</v>
       </c>
       <c r="J15" t="n">
-        <v>31.8298</v>
+        <v>1.0228</v>
       </c>
       <c r="K15" t="n">
-        <v>16.1958</v>
+        <v>0.9824000000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>15.6337</v>
+        <v>0.0405</v>
       </c>
       <c r="M15" t="n">
-        <v>-34.4417</v>
+        <v>-1.2188</v>
       </c>
       <c r="N15" t="n">
-        <v>-24.9843</v>
+        <v>-0.2745</v>
       </c>
       <c r="O15" t="n">
-        <v>-9.457699999999999</v>
+        <v>-0.9443</v>
       </c>
       <c r="P15" t="n">
-        <v>-4.883399999999999</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q15" t="n">
-        <v>-49.8122</v>
+        <v>-0.9767</v>
       </c>
       <c r="R15" t="n">
-        <v>44.9288</v>
+        <v>0.586</v>
       </c>
       <c r="S15" t="n">
-        <v>-10.629</v>
+        <v>0.2683</v>
       </c>
       <c r="T15" t="n">
-        <v>-5.4667</v>
+        <v>0.2972</v>
       </c>
       <c r="U15" t="n">
-        <v>-5.1619</v>
+        <v>-0.0289</v>
       </c>
       <c r="V15" t="n">
-        <v>16.5235</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>20.8839</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-4.3606</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>I. MASPONS MOLINS</t>
+          <t>E. VAZQUEZ MARESMA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-3.5362</v>
+        <v>-0.3185</v>
       </c>
       <c r="E16" t="n">
-        <v>-6.966299999999999</v>
+        <v>-0.7185</v>
       </c>
       <c r="F16" t="n">
-        <v>3.430099999999999</v>
+        <v>0.4</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.948199999999999</v>
+        <v>0.3617</v>
       </c>
       <c r="H16" t="n">
-        <v>2.6282</v>
+        <v>-0.2589</v>
       </c>
       <c r="I16" t="n">
-        <v>-4.5764</v>
+        <v>0.6206</v>
       </c>
       <c r="J16" t="n">
-        <v>14.3276</v>
+        <v>0.6413</v>
       </c>
       <c r="K16" t="n">
-        <v>11.0718</v>
+        <v>0.0205</v>
       </c>
       <c r="L16" t="n">
-        <v>3.2561</v>
+        <v>0.6208</v>
       </c>
       <c r="M16" t="n">
-        <v>-16.2759</v>
+        <v>-0.2795</v>
       </c>
       <c r="N16" t="n">
-        <v>-8.443899999999999</v>
+        <v>-0.2793</v>
       </c>
       <c r="O16" t="n">
-        <v>-7.8323</v>
+        <v>-0.0002</v>
       </c>
       <c r="P16" t="n">
-        <v>-2.9301</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q16" t="n">
-        <v>-25.199</v>
+        <v>-0.9767</v>
       </c>
       <c r="R16" t="n">
-        <v>22.2691</v>
+        <v>0.7814</v>
       </c>
       <c r="S16" t="n">
-        <v>1.8301</v>
+        <v>-0.4849</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3008</v>
+        <v>-0.3831</v>
       </c>
       <c r="U16" t="n">
-        <v>1.5292</v>
+        <v>-0.1018</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.4881</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>3.6039</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-4.092000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. MARTÍN ADELANTADO</t>
+          <t>F. REYES ARANDA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,76 +1732,76 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>-6.0782</v>
+        <v>-1.1469</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.3617000000000006</v>
+        <v>-1.8014</v>
       </c>
       <c r="F17" t="n">
-        <v>-5.7163</v>
+        <v>0.6542</v>
       </c>
       <c r="G17" t="n">
-        <v>-12.4205</v>
+        <v>-0.7487999999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>-6.3161</v>
+        <v>-2.4341</v>
       </c>
       <c r="I17" t="n">
-        <v>-6.1044</v>
+        <v>1.6854</v>
       </c>
       <c r="J17" t="n">
-        <v>7.2849</v>
+        <v>-0.5240999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>3.9421</v>
+        <v>-1.9404</v>
       </c>
       <c r="L17" t="n">
-        <v>3.3428</v>
+        <v>1.4164</v>
       </c>
       <c r="M17" t="n">
-        <v>-19.7056</v>
+        <v>-0.2247</v>
       </c>
       <c r="N17" t="n">
-        <v>-10.2582</v>
+        <v>-0.4936999999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>-9.447199999999999</v>
+        <v>0.2691</v>
       </c>
       <c r="P17" t="n">
-        <v>5.4697</v>
+        <v>0.5859</v>
       </c>
       <c r="Q17" t="n">
-        <v>-8.7904</v>
+        <v>-1.172</v>
       </c>
       <c r="R17" t="n">
-        <v>14.2601</v>
+        <v>1.758</v>
       </c>
       <c r="S17" t="n">
-        <v>2.0919</v>
+        <v>-1.2614</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5343000000000001</v>
+        <v>-0.3822</v>
       </c>
       <c r="U17" t="n">
-        <v>1.5576</v>
+        <v>-0.8792</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.2191</v>
+        <v>0.2772</v>
       </c>
       <c r="W17" t="n">
-        <v>0.6093</v>
+        <v>0.2772</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.8285</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. TORNÉ DELAURENS</t>
+          <t>O. TOURE JABBY</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,76 +1810,76 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D18" t="n">
-        <v>-6.305</v>
+        <v>-1.353200000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>6.5419</v>
+        <v>-5.588399999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>-12.8466</v>
+        <v>4.235200000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>-19.5057</v>
+        <v>11.3571</v>
       </c>
       <c r="H18" t="n">
-        <v>-20.0598</v>
+        <v>11.4201</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5539000000000003</v>
+        <v>-0.06309999999999993</v>
       </c>
       <c r="J18" t="n">
-        <v>11.7742</v>
+        <v>30.4639</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8206000000000002</v>
+        <v>23.6351</v>
       </c>
       <c r="L18" t="n">
-        <v>10.9535</v>
+        <v>6.828899999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>-31.2795</v>
+        <v>-19.1068</v>
       </c>
       <c r="N18" t="n">
-        <v>-20.8803</v>
+        <v>-12.2147</v>
       </c>
       <c r="O18" t="n">
-        <v>-10.3992</v>
+        <v>-6.891900000000001</v>
       </c>
       <c r="P18" t="n">
-        <v>19.7296</v>
+        <v>-13.4787</v>
       </c>
       <c r="Q18" t="n">
-        <v>-15.0412</v>
+        <v>-43.7568</v>
       </c>
       <c r="R18" t="n">
-        <v>34.7711</v>
+        <v>30.2781</v>
       </c>
       <c r="S18" t="n">
-        <v>4.0867</v>
+        <v>3.192299999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>3.8775</v>
+        <v>0.6063999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2095000000000001</v>
+        <v>2.5856</v>
       </c>
       <c r="V18" t="n">
-        <v>-10.6161</v>
+        <v>-2.423900000000001</v>
       </c>
       <c r="W18" t="n">
-        <v>5.931099999999999</v>
+        <v>7.0982</v>
       </c>
       <c r="X18" t="n">
-        <v>-16.5473</v>
+        <v>-9.5221</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. PEIRO COSMO</t>
+          <t>M. BALLUS TORRAS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1888,76 +1888,76 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>-6.453600000000001</v>
+        <v>-2.4415</v>
       </c>
       <c r="E19" t="n">
-        <v>-4.329000000000001</v>
+        <v>-0.6933</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.1245</v>
+        <v>-1.7483</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.9527</v>
+        <v>-3.3488</v>
       </c>
       <c r="H19" t="n">
-        <v>1.5983</v>
+        <v>2.5992</v>
       </c>
       <c r="I19" t="n">
-        <v>-3.5505</v>
+        <v>-5.9479</v>
       </c>
       <c r="J19" t="n">
-        <v>9.0733</v>
+        <v>1.8913</v>
       </c>
       <c r="K19" t="n">
-        <v>8.0311</v>
+        <v>3.7913</v>
       </c>
       <c r="L19" t="n">
-        <v>1.0423</v>
+        <v>-1.8999</v>
       </c>
       <c r="M19" t="n">
-        <v>-11.0258</v>
+        <v>-5.2401</v>
       </c>
       <c r="N19" t="n">
-        <v>-6.433</v>
+        <v>-1.1921</v>
       </c>
       <c r="O19" t="n">
-        <v>-4.5931</v>
+        <v>-4.048</v>
       </c>
       <c r="P19" t="n">
-        <v>0.7813000000000001</v>
+        <v>0.3907</v>
       </c>
       <c r="Q19" t="n">
-        <v>-17.9712</v>
+        <v>-3.9068</v>
       </c>
       <c r="R19" t="n">
-        <v>18.7531</v>
+        <v>4.297499999999999</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2860000000000001</v>
+        <v>0.4835999999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>0.07839999999999997</v>
+        <v>0.4357</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3647</v>
+        <v>0.04799999999999998</v>
       </c>
       <c r="V19" t="n">
-        <v>-4.9962</v>
+        <v>0.03289999999999993</v>
       </c>
       <c r="W19" t="n">
-        <v>4.4904</v>
+        <v>0.8864999999999998</v>
       </c>
       <c r="X19" t="n">
-        <v>-9.486799999999999</v>
+        <v>-0.8535999999999999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>O. HERAS FLECHA</t>
+          <t>I. MASPONS MOLINS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1966,76 +1966,76 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D20" t="n">
-        <v>-9.1546</v>
+        <v>-3.5362</v>
       </c>
       <c r="E20" t="n">
-        <v>5.104600000000002</v>
+        <v>-6.966299999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>-14.2593</v>
+        <v>3.430099999999999</v>
       </c>
       <c r="G20" t="n">
-        <v>-10.1346</v>
+        <v>-1.948199999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>-5.1165</v>
+        <v>2.6282</v>
       </c>
       <c r="I20" t="n">
-        <v>-5.017900000000001</v>
+        <v>-4.5764</v>
       </c>
       <c r="J20" t="n">
-        <v>23.3241</v>
+        <v>14.3276</v>
       </c>
       <c r="K20" t="n">
-        <v>19.0201</v>
+        <v>11.0718</v>
       </c>
       <c r="L20" t="n">
-        <v>4.3043</v>
+        <v>3.2561</v>
       </c>
       <c r="M20" t="n">
-        <v>-33.4586</v>
+        <v>-16.2759</v>
       </c>
       <c r="N20" t="n">
-        <v>-24.1365</v>
+        <v>-8.443899999999999</v>
       </c>
       <c r="O20" t="n">
-        <v>-9.321999999999999</v>
+        <v>-7.8323</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.7815000000000001</v>
+        <v>-2.9301</v>
       </c>
       <c r="Q20" t="n">
-        <v>-40.8265</v>
+        <v>-25.199</v>
       </c>
       <c r="R20" t="n">
-        <v>40.0455</v>
+        <v>22.2691</v>
       </c>
       <c r="S20" t="n">
-        <v>-11.709</v>
+        <v>1.8301</v>
       </c>
       <c r="T20" t="n">
-        <v>-3.8732</v>
+        <v>0.3008</v>
       </c>
       <c r="U20" t="n">
-        <v>-7.8359</v>
+        <v>1.5292</v>
       </c>
       <c r="V20" t="n">
-        <v>13.471</v>
+        <v>-0.4881</v>
       </c>
       <c r="W20" t="n">
-        <v>26.4808</v>
+        <v>3.6039</v>
       </c>
       <c r="X20" t="n">
-        <v>-13.0098</v>
+        <v>-4.092000000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. JUAREZ GIMENEZ</t>
+          <t>A. PEIRO COSMO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2044,76 +2044,76 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="D21" t="n">
-        <v>-13.7192</v>
+        <v>-6.453600000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>-16.4093</v>
+        <v>-4.329000000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>2.6899</v>
+        <v>-2.1245</v>
       </c>
       <c r="G21" t="n">
-        <v>-15.9332</v>
+        <v>-1.9527</v>
       </c>
       <c r="H21" t="n">
-        <v>-18.2347</v>
+        <v>1.5983</v>
       </c>
       <c r="I21" t="n">
-        <v>2.302</v>
+        <v>-3.5505</v>
       </c>
       <c r="J21" t="n">
-        <v>7.786799999999999</v>
+        <v>9.0733</v>
       </c>
       <c r="K21" t="n">
-        <v>-3.028900000000001</v>
+        <v>8.0311</v>
       </c>
       <c r="L21" t="n">
-        <v>10.8151</v>
+        <v>1.0423</v>
       </c>
       <c r="M21" t="n">
-        <v>-23.7199</v>
+        <v>-11.0258</v>
       </c>
       <c r="N21" t="n">
-        <v>-15.2061</v>
+        <v>-6.433</v>
       </c>
       <c r="O21" t="n">
-        <v>-8.513500000000001</v>
+        <v>-4.5931</v>
       </c>
       <c r="P21" t="n">
-        <v>-9.376300000000001</v>
+        <v>0.7813000000000001</v>
       </c>
       <c r="Q21" t="n">
-        <v>-53.7189</v>
+        <v>-17.9712</v>
       </c>
       <c r="R21" t="n">
-        <v>44.343</v>
+        <v>18.7531</v>
       </c>
       <c r="S21" t="n">
-        <v>-4.871700000000001</v>
+        <v>-0.2860000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.6672</v>
+        <v>0.07839999999999997</v>
       </c>
       <c r="U21" t="n">
-        <v>-3.2044</v>
+        <v>-0.3647</v>
       </c>
       <c r="V21" t="n">
-        <v>16.4618</v>
+        <v>-4.9962</v>
       </c>
       <c r="W21" t="n">
-        <v>31.1906</v>
+        <v>4.4904</v>
       </c>
       <c r="X21" t="n">
-        <v>-14.7288</v>
+        <v>-9.486799999999999</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. SALMERON SEGU</t>
+          <t>O. HERAS FLECHA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2122,76 +2122,76 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D22" t="n">
-        <v>-14.3955</v>
+        <v>-9.1546</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.673400000000001</v>
+        <v>5.104600000000002</v>
       </c>
       <c r="F22" t="n">
-        <v>-8.722100000000001</v>
+        <v>-14.2593</v>
       </c>
       <c r="G22" t="n">
-        <v>-12.0746</v>
+        <v>-10.1346</v>
       </c>
       <c r="H22" t="n">
-        <v>-4.1284</v>
+        <v>-5.1165</v>
       </c>
       <c r="I22" t="n">
-        <v>-7.945699999999999</v>
+        <v>-5.017900000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>14.0221</v>
+        <v>23.3241</v>
       </c>
       <c r="K22" t="n">
-        <v>12.2444</v>
+        <v>19.0201</v>
       </c>
       <c r="L22" t="n">
-        <v>1.7774</v>
+        <v>4.3043</v>
       </c>
       <c r="M22" t="n">
-        <v>-26.0964</v>
+        <v>-33.4586</v>
       </c>
       <c r="N22" t="n">
-        <v>-16.3729</v>
+        <v>-24.1365</v>
       </c>
       <c r="O22" t="n">
-        <v>-9.7239</v>
+        <v>-9.321999999999999</v>
       </c>
       <c r="P22" t="n">
-        <v>5.8605</v>
+        <v>-0.7815000000000001</v>
       </c>
       <c r="Q22" t="n">
-        <v>-23.6363</v>
+        <v>-40.8265</v>
       </c>
       <c r="R22" t="n">
-        <v>29.4971</v>
+        <v>40.0455</v>
       </c>
       <c r="S22" t="n">
-        <v>2.9486</v>
+        <v>-11.709</v>
       </c>
       <c r="T22" t="n">
-        <v>1.8848</v>
+        <v>-3.8732</v>
       </c>
       <c r="U22" t="n">
-        <v>1.0638</v>
+        <v>-7.8359</v>
       </c>
       <c r="V22" t="n">
-        <v>-11.13</v>
+        <v>13.471</v>
       </c>
       <c r="W22" t="n">
-        <v>2.055899999999999</v>
+        <v>26.4808</v>
       </c>
       <c r="X22" t="n">
-        <v>-13.186</v>
+        <v>-13.0098</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>J. JUAREZ GIMENEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,66 +2203,456 @@
         <v>26</v>
       </c>
       <c r="D23" t="n">
-        <v>-41.33240000000001</v>
+        <v>-13.7192</v>
       </c>
       <c r="E23" t="n">
-        <v>8.218199999999992</v>
+        <v>-16.4093</v>
       </c>
       <c r="F23" t="n">
-        <v>-49.55110000000001</v>
+        <v>2.6899</v>
       </c>
       <c r="G23" t="n">
-        <v>-81.3349</v>
+        <v>-15.9332</v>
       </c>
       <c r="H23" t="n">
-        <v>-63.8168</v>
+        <v>-18.2347</v>
       </c>
       <c r="I23" t="n">
-        <v>-17.5166</v>
+        <v>2.302</v>
       </c>
       <c r="J23" t="n">
-        <v>209.5115</v>
+        <v>7.786799999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>123.0219</v>
+        <v>-3.028900000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>86.4898</v>
+        <v>10.8151</v>
       </c>
       <c r="M23" t="n">
+        <v>-23.7199</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-15.2061</v>
+      </c>
+      <c r="O23" t="n">
+        <v>-8.513500000000001</v>
+      </c>
+      <c r="P23" t="n">
+        <v>-9.376300000000001</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>-53.7189</v>
+      </c>
+      <c r="R23" t="n">
+        <v>44.343</v>
+      </c>
+      <c r="S23" t="n">
+        <v>-4.871700000000001</v>
+      </c>
+      <c r="T23" t="n">
+        <v>-1.6672</v>
+      </c>
+      <c r="U23" t="n">
+        <v>-3.2044</v>
+      </c>
+      <c r="V23" t="n">
+        <v>16.4618</v>
+      </c>
+      <c r="W23" t="n">
+        <v>31.1906</v>
+      </c>
+      <c r="X23" t="n">
+        <v>-14.7288</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>M. SALMERON SEGU</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>C.B. GRANOLLERS</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>24</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-14.3955</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-5.673400000000001</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-8.722100000000001</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-12.0746</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-4.1284</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-7.945699999999999</v>
+      </c>
+      <c r="J24" t="n">
+        <v>14.0221</v>
+      </c>
+      <c r="K24" t="n">
+        <v>12.2444</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.7774</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-26.0964</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-16.3729</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-9.7239</v>
+      </c>
+      <c r="P24" t="n">
+        <v>5.8605</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-23.6363</v>
+      </c>
+      <c r="R24" t="n">
+        <v>29.4971</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.9486</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.8848</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.0638</v>
+      </c>
+      <c r="V24" t="n">
+        <v>-11.13</v>
+      </c>
+      <c r="W24" t="n">
+        <v>2.055899999999999</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-13.186</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>A. MARTIN ADELANTADO</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>C.B. GRANOLLERS</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>15</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-16.1388</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-10.4225</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-5.7163</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-22.4812</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-10.3069</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-12.1743</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-2.7755</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-0.04870000000000019</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-2.727000000000001</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-19.7056</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-10.2582</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-9.447199999999999</v>
+      </c>
+      <c r="P25" t="n">
+        <v>5.4697</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-8.7904</v>
+      </c>
+      <c r="R25" t="n">
+        <v>14.2601</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.0919</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.5343000000000001</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.5576</v>
+      </c>
+      <c r="V25" t="n">
+        <v>-1.2191</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0.6093</v>
+      </c>
+      <c r="X25" t="n">
+        <v>-1.8285</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>M. TORNE DELAURENS</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>C.B. GRANOLLERS</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>25</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-17.5654</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-4.7189</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-12.8466</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-30.7663</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-22.8228</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-7.943899999999999</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.5134</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-1.9423</v>
+      </c>
+      <c r="L26" t="n">
+        <v>2.4561</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-31.2795</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-20.8803</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-10.3992</v>
+      </c>
+      <c r="P26" t="n">
+        <v>19.7296</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-15.0412</v>
+      </c>
+      <c r="R26" t="n">
+        <v>34.7711</v>
+      </c>
+      <c r="S26" t="n">
+        <v>4.0867</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3.8775</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0.2095000000000001</v>
+      </c>
+      <c r="V26" t="n">
+        <v>-10.6161</v>
+      </c>
+      <c r="W26" t="n">
+        <v>5.931099999999999</v>
+      </c>
+      <c r="X26" t="n">
+        <v>-16.5473</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>A. VINALLONGA GOMEZ</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>C.B. GRANOLLERS</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>24</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-27.8693</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-28.8336</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.9645999999999995</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-28.8804</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-23.5237</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-5.3568</v>
+      </c>
+      <c r="J27" t="n">
+        <v>5.561199999999998</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1.4606</v>
+      </c>
+      <c r="L27" t="n">
+        <v>4.100900000000001</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-34.4417</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-24.9843</v>
+      </c>
+      <c r="O27" t="n">
+        <v>-9.457699999999999</v>
+      </c>
+      <c r="P27" t="n">
+        <v>-4.883399999999999</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>-49.8122</v>
+      </c>
+      <c r="R27" t="n">
+        <v>44.9288</v>
+      </c>
+      <c r="S27" t="n">
+        <v>-10.629</v>
+      </c>
+      <c r="T27" t="n">
+        <v>-5.4667</v>
+      </c>
+      <c r="U27" t="n">
+        <v>-5.1619</v>
+      </c>
+      <c r="V27" t="n">
+        <v>16.5235</v>
+      </c>
+      <c r="W27" t="n">
+        <v>20.8839</v>
+      </c>
+      <c r="X27" t="n">
+        <v>-4.3606</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>C.B. GRANOLLERS</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>26</v>
+      </c>
+      <c r="D28" t="n">
+        <v>-41.33180000000001</v>
+      </c>
+      <c r="E28" t="n">
+        <v>8.218500000000002</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-49.5511</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-81.33410000000001</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-63.8161</v>
+      </c>
+      <c r="I28" t="n">
+        <v>-17.51629999999999</v>
+      </c>
+      <c r="J28" t="n">
+        <v>209.5117</v>
+      </c>
+      <c r="K28" t="n">
+        <v>123.0226</v>
+      </c>
+      <c r="L28" t="n">
+        <v>86.4906</v>
+      </c>
+      <c r="M28" t="n">
         <v>-290.8452</v>
       </c>
-      <c r="N23" t="n">
+      <c r="N28" t="n">
         <v>-186.8398</v>
       </c>
-      <c r="O23" t="n">
+      <c r="O28" t="n">
         <v>-104.0069</v>
       </c>
-      <c r="P23" t="n">
+      <c r="P28" t="n">
         <v>18.5579</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="Q28" t="n">
         <v>-366.265</v>
       </c>
-      <c r="R23" t="n">
+      <c r="R28" t="n">
         <v>384.8262</v>
       </c>
-      <c r="S23" t="n">
+      <c r="S28" t="n">
         <v>-13.1689</v>
       </c>
-      <c r="T23" t="n">
+      <c r="T28" t="n">
         <v>-1.421399999999999</v>
       </c>
-      <c r="U23" t="n">
+      <c r="U28" t="n">
         <v>-11.7474</v>
       </c>
-      <c r="V23" t="n">
-        <v>34.61240000000001</v>
-      </c>
-      <c r="W23" t="n">
+      <c r="V28" t="n">
+        <v>34.61239999999999</v>
+      </c>
+      <c r="W28" t="n">
         <v>166.3944</v>
       </c>
-      <c r="X23" t="n">
+      <c r="X28" t="n">
         <v>-131.783</v>
       </c>
     </row>
